--- a/modelo-importacao-capacidade.xlsx
+++ b/modelo-importacao-capacidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vagner.moraes\Documents\Project_VS\DEV_PLAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B752A328-5144-4740-B1AC-38AA326B31A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B168BD-C524-491A-B7BB-97BC1EA2815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29409A3D-ECD3-417C-94F1-78FDE07D3DC8}"/>
   </bookViews>
@@ -409,18 +409,6 @@
     <t>Horas alocadas</t>
   </si>
   <si>
-    <t>NEXUS</t>
-  </si>
-  <si>
-    <t>HOUSE OF CARGO</t>
-  </si>
-  <si>
-    <t>EVOLUTION</t>
-  </si>
-  <si>
-    <t>LONE STAR</t>
-  </si>
-  <si>
     <t>DEV</t>
   </si>
   <si>
@@ -431,6 +419,18 @@
   </si>
   <si>
     <t>ESPECIALISTA</t>
+  </si>
+  <si>
+    <t>nddElog</t>
+  </si>
+  <si>
+    <t>nddFrete</t>
+  </si>
+  <si>
+    <t>nddMove</t>
+  </si>
+  <si>
+    <t>nddCargo</t>
   </si>
 </sst>
 </file>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D2" s="4">
         <v>130</v>
@@ -887,10 +887,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D3" s="4">
         <v>130</v>
@@ -904,10 +904,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" s="4">
         <v>130</v>
@@ -921,10 +921,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D5" s="4">
         <v>130</v>
@@ -938,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="D6" s="4">
         <v>130</v>
@@ -955,10 +955,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7" s="4">
         <v>130</v>
@@ -972,10 +972,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D8" s="4">
         <v>130</v>
@@ -989,10 +989,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D9" s="4">
         <v>130</v>
@@ -1006,10 +1006,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10" s="4">
         <v>130</v>
@@ -1023,10 +1023,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D11" s="4">
         <v>130</v>
@@ -1040,10 +1040,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D12" s="4">
         <v>130</v>
@@ -1057,10 +1057,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" s="4">
         <v>130</v>
@@ -1074,10 +1074,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D14" s="4">
         <v>130</v>
@@ -1091,10 +1091,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D15" s="4">
         <v>130</v>
@@ -1108,10 +1108,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D16" s="4">
         <v>130</v>
@@ -1125,10 +1125,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4">
         <v>130</v>
@@ -1142,10 +1142,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D18" s="4">
         <v>130</v>
@@ -1159,10 +1159,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="D19" s="4">
         <v>130</v>
@@ -1176,10 +1176,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D20" s="4">
         <v>130</v>
@@ -1193,10 +1193,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D21" s="4">
         <v>130</v>
@@ -1210,10 +1210,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D22" s="4">
         <v>130</v>
@@ -1227,10 +1227,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D23" s="4">
         <v>130</v>
@@ -1244,10 +1244,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D24" s="4">
         <v>130</v>
@@ -1261,10 +1261,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D25" s="4">
         <v>130</v>
@@ -1278,10 +1278,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D26" s="4">
         <v>130</v>
@@ -1295,10 +1295,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D27" s="4">
         <v>130</v>
@@ -1312,10 +1312,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D28" s="4">
         <v>130</v>
@@ -1329,10 +1329,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D29" s="4">
         <v>130</v>
@@ -1346,10 +1346,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D30" s="4">
         <v>130</v>
@@ -1363,10 +1363,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D31" s="4">
         <v>130</v>
@@ -1380,10 +1380,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D32" s="4">
         <v>130</v>
@@ -1397,10 +1397,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D33" s="4">
         <v>130</v>
@@ -1414,10 +1414,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D34" s="4">
         <v>130</v>
@@ -1431,10 +1431,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D35" s="4">
         <v>130</v>
@@ -1448,10 +1448,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D36" s="4">
         <v>130</v>
